--- a/Assets/Data/Excel/NpcTable.xlsx
+++ b/Assets/Data/Excel/NpcTable.xlsx
@@ -1,45 +1,101 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\Work\UnityProject\MadHatter\Assets\Data\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FB3EEC-D16C-46D3-AE3D-939046F980D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NpcTable" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="NpcTable" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>uniqueId</t>
+  </si>
+  <si>
+    <t>npcName</t>
+  </si>
+  <si>
+    <t>defaultDialogueId</t>
+  </si>
+  <si>
+    <t>questId</t>
+  </si>
+  <si>
+    <t>NPC_001</t>
+  </si>
+  <si>
+    <t>마을 이장</t>
+  </si>
+  <si>
+    <t>DLG_001</t>
+  </si>
+  <si>
+    <t>QST_001</t>
+  </si>
+  <si>
+    <t>NPC_002</t>
+  </si>
+  <si>
+    <t>대장장이</t>
+  </si>
+  <si>
+    <t>DLG_005</t>
+  </si>
+  <si>
+    <t>QST_003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -52,96 +108,46 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -429,87 +435,60 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>uniqueId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>npcName</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>defaultDialogueId</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>questId</t>
-        </is>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>NPC_001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>마을 이장</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>DLG_001</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>QST_001</t>
-        </is>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>NPC_002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>대장장이</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>DLG_005</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>QST_002</t>
-        </is>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Assets/Data/Excel/NpcTable.xlsx
+++ b/Assets/Data/Excel/NpcTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\Work\UnityProject\MadHatter\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FB3EEC-D16C-46D3-AE3D-939046F980D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D16A343-33A8-4D12-A3E3-B378B85C02CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="180" windowWidth="28800" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NpcTable" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
     <t>DLG_005</t>
   </si>
   <si>
-    <t>QST_003</t>
+    <t>QST_002</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/Assets/Data/Excel/NpcTable.xlsx
+++ b/Assets/Data/Excel/NpcTable.xlsx
@@ -1,94 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\Work\UnityProject\MadHatter\Assets\Data\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D16A343-33A8-4D12-A3E3-B378B85C02CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="180" windowWidth="28800" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="780" windowWidth="28800" windowHeight="15420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NpcTable" sheetId="1" r:id="rId1"/>
+    <sheet name="NpcTable" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>uniqueId</t>
-  </si>
-  <si>
-    <t>npcName</t>
-  </si>
-  <si>
-    <t>defaultDialogueId</t>
-  </si>
-  <si>
-    <t>questId</t>
-  </si>
-  <si>
-    <t>NPC_001</t>
-  </si>
-  <si>
-    <t>마을 이장</t>
-  </si>
-  <si>
-    <t>DLG_001</t>
-  </si>
-  <si>
-    <t>QST_001</t>
-  </si>
-  <si>
-    <t>NPC_002</t>
-  </si>
-  <si>
-    <t>대장장이</t>
-  </si>
-  <si>
-    <t>DLG_005</t>
-  </si>
-  <si>
-    <t>QST_002</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -127,27 +80,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -435,60 +447,116 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>uniqueId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>npcName</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>defaultDialogueId</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>questId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>shopId</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>NPC_001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>마을 이장</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>DLG_001</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>QST_001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>NPC_002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>대장장이</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>DLG_005</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>QST_002</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NPC_003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>상점 주인</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DLG_SHOP</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SHOP_001</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Assets/Data/Excel/NpcTable.xlsx
+++ b/Assets/Data/Excel/NpcTable.xlsx
@@ -6,53 +6,92 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="780" windowWidth="28800" windowHeight="15420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NpcTable" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="NpcTable" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>uniqueId</t>
+  </si>
+  <si>
+    <t>npcName</t>
+  </si>
+  <si>
+    <t>defaultDialogueId</t>
+  </si>
+  <si>
+    <t>questId</t>
+  </si>
+  <si>
+    <t>shopId</t>
+  </si>
+  <si>
+    <t>NPC_001</t>
+  </si>
+  <si>
+    <t>마을 이장</t>
+  </si>
+  <si>
+    <t>DLG_DEFAULT_ELDER</t>
+  </si>
+  <si>
+    <t>QST_001</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>NPC_002</t>
+  </si>
+  <si>
+    <t>대장장이</t>
+  </si>
+  <si>
+    <t>DLG_DEFAULT_SMITH</t>
+  </si>
+  <si>
+    <t>QST_002</t>
+  </si>
+  <si>
+    <t>NPC_003</t>
+  </si>
+  <si>
+    <t>상점 주인</t>
+  </si>
+  <si>
+    <t>DLG_SHOP</t>
+  </si>
+  <si>
+    <t>SHOP_001</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,33 +99,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -454,109 +473,77 @@
   </sheetPr>
   <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>uniqueId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>npcName</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>defaultDialogueId</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>questId</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>shopId</t>
-        </is>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>NPC_001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>마을 이장</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>DLG_001</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>QST_001</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>NPC_002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>대장장이</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>DLG_005</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>QST_002</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NPC_003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>상점 주인</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DLG_SHOP</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SHOP_001</t>
-        </is>
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>